--- a/Calificaciones20241.xlsx
+++ b/Calificaciones20241.xlsx
@@ -18090,7 +18090,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -18179,7 +18179,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -18268,7 +18268,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -18357,7 +18357,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -18399,7 +18399,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -18446,7 +18446,7 @@
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -18488,7 +18488,7 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -18535,7 +18535,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -18624,7 +18624,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -18713,7 +18713,7 @@
         <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -18802,7 +18802,7 @@
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -18891,7 +18891,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -18980,7 +18980,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -19022,7 +19022,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -19069,7 +19069,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -19158,7 +19158,7 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -19200,7 +19200,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -19247,7 +19247,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -19289,7 +19289,7 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -19336,7 +19336,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -19378,7 +19378,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -19425,7 +19425,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -19514,7 +19514,7 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -19603,7 +19603,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -19645,7 +19645,7 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -19692,7 +19692,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -19781,7 +19781,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -19823,7 +19823,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -19870,7 +19870,7 @@
         <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -19959,7 +19959,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -20001,7 +20001,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>9</v>
@@ -20048,7 +20048,7 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -20137,7 +20137,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -20179,7 +20179,7 @@
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -20226,7 +20226,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -20315,7 +20315,7 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -20404,7 +20404,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -20493,7 +20493,7 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -20715,7 +20715,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -20751,7 +20751,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -20792,7 +20792,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -20828,7 +20828,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -20869,7 +20869,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -20905,7 +20905,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -20946,7 +20946,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -20982,7 +20982,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -21023,7 +21023,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -21100,7 +21100,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -21177,7 +21177,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -21213,7 +21213,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -21254,7 +21254,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -21290,7 +21290,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -21331,7 +21331,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -21367,7 +21367,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -21408,7 +21408,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -21444,7 +21444,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -21485,7 +21485,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -21562,7 +21562,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>8</v>
@@ -21598,7 +21598,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -21639,7 +21639,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -21675,7 +21675,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -21716,7 +21716,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -21752,7 +21752,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -21793,7 +21793,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -21829,7 +21829,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -21870,7 +21870,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -21906,7 +21906,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -21947,7 +21947,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -22024,7 +22024,7 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -22060,7 +22060,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -22101,7 +22101,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -22137,7 +22137,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -22178,7 +22178,7 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>7</v>
@@ -22214,7 +22214,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -22255,7 +22255,7 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -22332,7 +22332,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -22409,7 +22409,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -22445,7 +22445,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -22486,7 +22486,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>6</v>
@@ -22522,7 +22522,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -22563,7 +22563,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -22640,7 +22640,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -22676,7 +22676,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -22717,7 +22717,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>8</v>
@@ -22753,7 +22753,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -22794,7 +22794,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -22871,7 +22871,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -22907,7 +22907,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -22948,7 +22948,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -22984,7 +22984,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -23025,7 +23025,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>9</v>
@@ -23102,7 +23102,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>8</v>
@@ -23138,7 +23138,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -23179,7 +23179,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -23215,7 +23215,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -23256,7 +23256,7 @@
         <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>7</v>
@@ -23333,7 +23333,7 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>10</v>
@@ -23410,7 +23410,7 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
         <v>9</v>
@@ -23446,7 +23446,7 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -23487,7 +23487,7 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>8</v>
@@ -23523,7 +23523,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -23564,7 +23564,7 @@
         <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
         <v>10</v>
@@ -23641,7 +23641,7 @@
         <v>9</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
         <v>8</v>
@@ -23677,7 +23677,7 @@
         <v>9</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X42">
         <v>9</v>
@@ -23718,7 +23718,7 @@
         <v>10</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
         <v>7</v>
@@ -23754,7 +23754,7 @@
         <v>10</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>9</v>
@@ -23795,7 +23795,7 @@
         <v>10</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
         <v>10</v>
@@ -24011,7 +24011,7 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -24088,7 +24088,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -24165,7 +24165,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -24201,7 +24201,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -24242,7 +24242,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -24278,7 +24278,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -24319,7 +24319,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -24355,7 +24355,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -24396,7 +24396,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -24432,7 +24432,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -24473,7 +24473,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -24509,7 +24509,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -24550,7 +24550,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -24586,7 +24586,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -24627,7 +24627,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>7</v>
@@ -24663,7 +24663,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -24704,7 +24704,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -24781,7 +24781,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -24817,7 +24817,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -24858,7 +24858,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -24894,7 +24894,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -24935,7 +24935,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>7</v>
@@ -24971,7 +24971,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -25012,7 +25012,7 @@
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -25048,7 +25048,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -25089,7 +25089,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -25125,7 +25125,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -25166,7 +25166,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -25202,7 +25202,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -25243,7 +25243,7 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -25320,7 +25320,7 @@
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -25356,7 +25356,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -25397,7 +25397,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -25433,7 +25433,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -25474,7 +25474,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -25510,7 +25510,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -25551,7 +25551,7 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -25628,7 +25628,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -25705,7 +25705,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -25782,7 +25782,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -25859,7 +25859,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -25895,7 +25895,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -25936,7 +25936,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -25972,7 +25972,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -26013,7 +26013,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -26049,7 +26049,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -26090,7 +26090,7 @@
         <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -26126,7 +26126,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -26167,7 +26167,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -26244,7 +26244,7 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -26280,7 +26280,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -26321,7 +26321,7 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -26398,7 +26398,7 @@
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>6</v>
@@ -26434,7 +26434,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -26475,7 +26475,7 @@
         <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -26511,7 +26511,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -26552,7 +26552,7 @@
         <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -26795,7 +26795,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -26836,7 +26836,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -26872,7 +26872,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -26913,7 +26913,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -26949,7 +26949,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -26990,7 +26990,7 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -27026,7 +27026,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -27067,7 +27067,7 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -27144,7 +27144,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -27257,7 +27257,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -27298,7 +27298,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -27334,7 +27334,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -27375,7 +27375,7 @@
         <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -27411,7 +27411,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -27452,7 +27452,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -27529,7 +27529,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -27565,7 +27565,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -27606,7 +27606,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -27642,7 +27642,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -27760,7 +27760,7 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>6</v>
@@ -27837,7 +27837,7 @@
         <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>8</v>
@@ -27914,7 +27914,7 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>6</v>
@@ -27950,7 +27950,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -27991,7 +27991,7 @@
         <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -28027,7 +28027,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -28068,7 +28068,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -28104,7 +28104,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -28145,7 +28145,7 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>9</v>
@@ -28222,7 +28222,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>8</v>
@@ -28258,7 +28258,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -28299,7 +28299,7 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>7</v>
@@ -28376,7 +28376,7 @@
         <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -28453,7 +28453,7 @@
         <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -28530,7 +28530,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -28607,7 +28607,7 @@
         <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -28684,7 +28684,7 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -28761,7 +28761,7 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -28838,7 +28838,7 @@
         <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>7</v>
@@ -28874,7 +28874,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -28915,7 +28915,7 @@
         <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>6</v>
@@ -28992,7 +28992,7 @@
         <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -29069,7 +29069,7 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>10</v>
@@ -29105,7 +29105,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -29146,7 +29146,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>10</v>
@@ -29223,7 +29223,7 @@
         <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>7</v>
@@ -29259,7 +29259,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -29300,7 +29300,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
         <v>10</v>
@@ -29336,7 +29336,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -29377,7 +29377,7 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>10</v>
@@ -29413,7 +29413,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -29454,7 +29454,7 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>9</v>
@@ -29490,7 +29490,7 @@
         <v>9</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>9</v>
@@ -29531,7 +29531,7 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>10</v>
@@ -29608,7 +29608,7 @@
         <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
         <v>10</v>
@@ -29644,7 +29644,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -29685,7 +29685,7 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K42">
         <v>10</v>
@@ -29721,7 +29721,7 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W42">
         <v>10</v>
@@ -29762,7 +29762,7 @@
         <v>6</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>7</v>
@@ -29997,7 +29997,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -30086,7 +30086,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -30175,7 +30175,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -30264,7 +30264,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -30306,7 +30306,7 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -30353,7 +30353,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -30395,7 +30395,7 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -30442,7 +30442,7 @@
         <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -30484,7 +30484,7 @@
         <v>8</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -30531,7 +30531,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -30620,7 +30620,7 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -30709,7 +30709,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -30798,7 +30798,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -30840,7 +30840,7 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -30887,7 +30887,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -30929,7 +30929,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -30976,7 +30976,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -31018,7 +31018,7 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -31065,7 +31065,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -31154,7 +31154,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -31196,7 +31196,7 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>6</v>
@@ -31243,7 +31243,7 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -31285,7 +31285,7 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -31332,7 +31332,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -31421,7 +31421,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -31510,7 +31510,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -31599,7 +31599,7 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -31641,7 +31641,7 @@
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>6</v>
@@ -31688,7 +31688,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -31777,7 +31777,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -31819,7 +31819,7 @@
         <v>6</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -31866,7 +31866,7 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -31955,7 +31955,7 @@
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -32044,7 +32044,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -32133,7 +32133,7 @@
         <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -32175,7 +32175,7 @@
         <v>6</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -32222,7 +32222,7 @@
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -32264,7 +32264,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>9</v>
@@ -32311,7 +32311,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -32400,7 +32400,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -32442,7 +32442,7 @@
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>6</v>
@@ -32489,7 +32489,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -32578,7 +32578,7 @@
         <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>8</v>
@@ -32667,7 +32667,7 @@
         <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>8</v>
@@ -32709,7 +32709,7 @@
         <v>8</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -32889,7 +32889,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -32925,7 +32925,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -32966,7 +32966,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -33002,7 +33002,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -33043,7 +33043,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -33079,7 +33079,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -33120,7 +33120,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -33156,7 +33156,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -33197,7 +33197,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -33233,7 +33233,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -33274,7 +33274,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -33351,7 +33351,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -33387,7 +33387,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -33428,7 +33428,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -33464,7 +33464,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -33505,7 +33505,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -33541,7 +33541,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -33582,7 +33582,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -33618,7 +33618,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -33659,7 +33659,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -33695,7 +33695,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -33736,7 +33736,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -33813,7 +33813,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -33849,7 +33849,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -33890,7 +33890,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -33926,7 +33926,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -33967,7 +33967,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -34003,7 +34003,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -34044,7 +34044,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -34121,7 +34121,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -34157,7 +34157,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -34198,7 +34198,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -34234,7 +34234,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -34275,7 +34275,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -34352,7 +34352,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -34388,7 +34388,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -34429,7 +34429,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -34465,7 +34465,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -34506,7 +34506,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -34542,7 +34542,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -34583,7 +34583,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -34660,7 +34660,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -34696,7 +34696,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -34737,7 +34737,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -34773,7 +34773,7 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -34814,7 +34814,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -34850,7 +34850,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -34891,7 +34891,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -34927,7 +34927,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -34968,7 +34968,7 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -35045,7 +35045,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -35081,7 +35081,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -35122,7 +35122,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -35158,7 +35158,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -35199,7 +35199,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -35235,7 +35235,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -35276,7 +35276,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -35312,7 +35312,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -35353,7 +35353,7 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -35389,7 +35389,7 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -35430,7 +35430,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -35507,7 +35507,7 @@
         <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>8</v>
@@ -35543,7 +35543,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -35584,7 +35584,7 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -35620,7 +35620,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -35847,7 +35847,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -35948,7 +35948,7 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -36049,7 +36049,7 @@
         <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -36150,7 +36150,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -36251,7 +36251,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -36352,7 +36352,7 @@
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -36453,7 +36453,7 @@
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -36554,7 +36554,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -36655,7 +36655,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -36756,7 +36756,7 @@
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -36857,7 +36857,7 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -36958,7 +36958,7 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -37059,7 +37059,7 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -37160,7 +37160,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -37261,7 +37261,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -37309,7 +37309,7 @@
         <v>5</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -37362,7 +37362,7 @@
         <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -37463,7 +37463,7 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -37564,7 +37564,7 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -37665,7 +37665,7 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -37766,7 +37766,7 @@
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -37867,7 +37867,7 @@
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -37968,7 +37968,7 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -38069,7 +38069,7 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -38170,7 +38170,7 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -38271,7 +38271,7 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -38319,7 +38319,7 @@
         <v>5</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:33">
@@ -38372,7 +38372,7 @@
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -38473,7 +38473,7 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -38574,7 +38574,7 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -38675,7 +38675,7 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -38776,7 +38776,7 @@
         <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -38877,7 +38877,7 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -38978,7 +38978,7 @@
         <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -39026,7 +39026,7 @@
         <v>6</v>
       </c>
       <c r="AG35">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:33">
@@ -39079,7 +39079,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -39180,7 +39180,7 @@
         <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -39228,7 +39228,7 @@
         <v>7</v>
       </c>
       <c r="AG37">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:33">
@@ -39281,7 +39281,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -39382,7 +39382,7 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -39430,7 +39430,7 @@
         <v>6</v>
       </c>
       <c r="AG39">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:33">
@@ -39483,7 +39483,7 @@
         <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -39584,7 +39584,7 @@
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -39673,7 +39673,7 @@
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -39762,7 +39762,7 @@
         <v>9</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -39986,7 +39986,7 @@
         <v>54</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -40010,7 +40010,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -40058,7 +40058,7 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -40087,7 +40087,7 @@
         <v>55</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -40111,7 +40111,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>8</v>
@@ -40159,7 +40159,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -40188,7 +40188,7 @@
         <v>56</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -40212,7 +40212,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -40260,7 +40260,7 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -40289,7 +40289,7 @@
         <v>57</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -40313,7 +40313,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -40361,7 +40361,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -40390,7 +40390,7 @@
         <v>58</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6.2</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -40414,7 +40414,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -40462,7 +40462,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -40491,7 +40491,7 @@
         <v>59</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -40515,7 +40515,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -40563,7 +40563,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -40592,7 +40592,7 @@
         <v>60</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6.8</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -40616,7 +40616,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -40664,7 +40664,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -40693,7 +40693,7 @@
         <v>61</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -40717,7 +40717,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -40765,7 +40765,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -40794,7 +40794,7 @@
         <v>62</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>8.5</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -40818,7 +40818,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -40866,7 +40866,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -40895,7 +40895,7 @@
         <v>63</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -40919,7 +40919,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -40967,7 +40967,7 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -40996,7 +40996,7 @@
         <v>64</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -41020,7 +41020,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -41068,7 +41068,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -41097,7 +41097,7 @@
         <v>65</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -41121,7 +41121,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>6</v>
@@ -41169,7 +41169,7 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -41198,7 +41198,7 @@
         <v>66</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -41222,7 +41222,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -41270,7 +41270,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>6</v>
@@ -41299,7 +41299,7 @@
         <v>67</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7.7</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -41323,7 +41323,7 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -41371,7 +41371,7 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -41400,7 +41400,7 @@
         <v>68</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6.8</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -41424,7 +41424,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>8</v>
@@ -41472,7 +41472,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -41501,7 +41501,7 @@
         <v>69</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7.3</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -41525,7 +41525,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -41573,7 +41573,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -41602,7 +41602,7 @@
         <v>70</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5.3</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -41626,7 +41626,7 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>5</v>
@@ -41674,7 +41674,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -41703,7 +41703,7 @@
         <v>71</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -41727,7 +41727,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -41775,7 +41775,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -41804,7 +41804,7 @@
         <v>72</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -41828,7 +41828,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>6</v>
@@ -41876,7 +41876,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>6</v>
@@ -41905,7 +41905,7 @@
         <v>73</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6.3</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -41929,7 +41929,7 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -41977,7 +41977,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -42006,7 +42006,7 @@
         <v>74</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6.8</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -42030,7 +42030,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -42078,7 +42078,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>7</v>
@@ -42107,7 +42107,7 @@
         <v>75</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -42131,7 +42131,7 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -42179,7 +42179,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -42208,7 +42208,7 @@
         <v>76</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6.2</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -42232,7 +42232,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -42280,7 +42280,7 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>5</v>
@@ -42309,7 +42309,7 @@
         <v>77</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>8</v>
@@ -42381,7 +42381,7 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -42410,7 +42410,7 @@
         <v>78</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>4.8</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -42434,7 +42434,7 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -42482,7 +42482,7 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -42511,7 +42511,7 @@
         <v>79</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -42535,7 +42535,7 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -42583,7 +42583,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -42612,7 +42612,7 @@
         <v>80</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -42636,7 +42636,7 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -42684,7 +42684,7 @@
         <v>-1</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -42713,7 +42713,7 @@
         <v>81</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -42737,7 +42737,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>6</v>
@@ -42785,7 +42785,7 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>6</v>
@@ -42814,7 +42814,7 @@
         <v>82</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -42838,7 +42838,7 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>8</v>
@@ -42886,7 +42886,7 @@
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>7</v>
@@ -42915,7 +42915,7 @@
         <v>83</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -42939,7 +42939,7 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>5</v>
@@ -42987,7 +42987,7 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>5</v>
@@ -43016,7 +43016,7 @@
         <v>84</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C34">
         <v>6</v>
@@ -43040,7 +43040,7 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>8</v>
@@ -43088,7 +43088,7 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -43117,7 +43117,7 @@
         <v>85</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -43141,7 +43141,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>5</v>
@@ -43189,7 +43189,7 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>5</v>
@@ -43218,7 +43218,7 @@
         <v>86</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -43242,7 +43242,7 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>7</v>
@@ -43290,7 +43290,7 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA36">
         <v>6</v>
@@ -43319,7 +43319,7 @@
         <v>87</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5.2</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -43343,7 +43343,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>7</v>
@@ -43391,7 +43391,7 @@
         <v>-1</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>6</v>
@@ -43420,7 +43420,7 @@
         <v>88</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>7.5</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -43444,7 +43444,7 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>6</v>
@@ -43492,7 +43492,7 @@
         <v>-1</v>
       </c>
       <c r="Z38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA38">
         <v>6</v>
@@ -43521,7 +43521,7 @@
         <v>89</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>6.2</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -43545,7 +43545,7 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>5</v>
@@ -43593,7 +43593,7 @@
         <v>-1</v>
       </c>
       <c r="Z39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA39">
         <v>5</v>
@@ -43622,7 +43622,7 @@
         <v>90</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>6.5</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -43646,7 +43646,7 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
         <v>6</v>
@@ -43694,7 +43694,7 @@
         <v>-1</v>
       </c>
       <c r="Z40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA40">
         <v>6</v>
@@ -43723,7 +43723,7 @@
         <v>91</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>7.8</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -43747,7 +43747,7 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K41">
         <v>8</v>
@@ -43795,7 +43795,7 @@
         <v>-1</v>
       </c>
       <c r="Z41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA41">
         <v>7</v>
@@ -43824,7 +43824,7 @@
         <v>92</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C42">
         <v>6</v>
@@ -43848,7 +43848,7 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
         <v>7</v>
@@ -43896,7 +43896,7 @@
         <v>-1</v>
       </c>
       <c r="Z42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA42">
         <v>7</v>
@@ -43925,7 +43925,7 @@
         <v>93</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -43949,7 +43949,7 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
         <v>7</v>
@@ -43997,7 +43997,7 @@
         <v>-1</v>
       </c>
       <c r="Z43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA43">
         <v>7</v>
@@ -44026,7 +44026,7 @@
         <v>94</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>7.8</v>
       </c>
       <c r="C44">
         <v>6</v>
@@ -44050,7 +44050,7 @@
         <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
         <v>8</v>
@@ -44098,7 +44098,7 @@
         <v>-1</v>
       </c>
       <c r="Z44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA44">
         <v>7</v>
@@ -44340,7 +44340,7 @@
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -44441,7 +44441,7 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -44542,7 +44542,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -44643,7 +44643,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -44744,7 +44744,7 @@
         <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -44792,7 +44792,7 @@
         <v>5</v>
       </c>
       <c r="AG8">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -44845,7 +44845,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -44946,7 +44946,7 @@
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -44994,7 +44994,7 @@
         <v>6</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -45047,7 +45047,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -45095,7 +45095,7 @@
         <v>6</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -45148,7 +45148,7 @@
         <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -45196,7 +45196,7 @@
         <v>8</v>
       </c>
       <c r="AG12">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -45249,7 +45249,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -45350,7 +45350,7 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -45398,7 +45398,7 @@
         <v>5</v>
       </c>
       <c r="AG14">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -45451,7 +45451,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -45552,7 +45552,7 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -45600,7 +45600,7 @@
         <v>5</v>
       </c>
       <c r="AG16">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:33">
@@ -45653,7 +45653,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -45701,7 +45701,7 @@
         <v>7</v>
       </c>
       <c r="AG17">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -45754,7 +45754,7 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -45802,7 +45802,7 @@
         <v>7</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -45855,7 +45855,7 @@
         <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -45956,7 +45956,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -46057,7 +46057,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -46158,7 +46158,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -46206,7 +46206,7 @@
         <v>8</v>
       </c>
       <c r="AG22">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:33">
@@ -46259,7 +46259,7 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -46360,7 +46360,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -46461,7 +46461,7 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -46562,7 +46562,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -46663,7 +46663,7 @@
         <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -46764,7 +46764,7 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -46865,7 +46865,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -46966,7 +46966,7 @@
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -47067,7 +47067,7 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -47168,7 +47168,7 @@
         <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -47216,7 +47216,7 @@
         <v>5</v>
       </c>
       <c r="AG32">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:33">
@@ -47269,7 +47269,7 @@
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -47370,7 +47370,7 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -47418,7 +47418,7 @@
         <v>5</v>
       </c>
       <c r="AG34">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:33">
@@ -47471,7 +47471,7 @@
         <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -47572,7 +47572,7 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -47673,7 +47673,7 @@
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -47921,7 +47921,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -47942,7 +47942,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -47969,7 +47969,7 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -47990,7 +47990,7 @@
         <v>7</v>
       </c>
       <c r="AG4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -48022,7 +48022,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -48043,7 +48043,7 @@
         <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -48070,7 +48070,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>5</v>
@@ -48091,7 +48091,7 @@
         <v>5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -48123,7 +48123,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -48144,7 +48144,7 @@
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -48171,7 +48171,7 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -48224,7 +48224,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -48245,7 +48245,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -48272,7 +48272,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -48325,7 +48325,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>7</v>
@@ -48346,7 +48346,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -48373,7 +48373,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>7</v>
@@ -48394,7 +48394,7 @@
         <v>5</v>
       </c>
       <c r="AG8">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -48426,7 +48426,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -48447,7 +48447,7 @@
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -48495,7 +48495,7 @@
         <v>5</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -48527,7 +48527,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -48548,7 +48548,7 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -48575,7 +48575,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>9</v>
@@ -48628,7 +48628,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -48649,7 +48649,7 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -48676,7 +48676,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -48750,7 +48750,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -48777,7 +48777,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>8</v>
@@ -48830,7 +48830,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -48851,7 +48851,7 @@
         <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -48931,7 +48931,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -48952,7 +48952,7 @@
         <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -48979,7 +48979,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -49032,7 +49032,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -49053,7 +49053,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -49133,7 +49133,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>7</v>
@@ -49154,7 +49154,7 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -49181,7 +49181,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -49234,7 +49234,7 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -49255,7 +49255,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -49282,7 +49282,7 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -49335,7 +49335,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -49356,7 +49356,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -49404,7 +49404,7 @@
         <v>5</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -49436,7 +49436,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -49457,7 +49457,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -49484,7 +49484,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -49505,7 +49505,7 @@
         <v>5</v>
       </c>
       <c r="AG19">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:33">
@@ -49537,7 +49537,7 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>6</v>
@@ -49558,7 +49558,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -49585,7 +49585,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>6</v>
@@ -49638,7 +49638,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>8</v>
@@ -49659,7 +49659,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -49686,7 +49686,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -49739,7 +49739,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -49760,7 +49760,7 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -49787,7 +49787,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -49840,7 +49840,7 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -49861,7 +49861,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -49888,7 +49888,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -49941,7 +49941,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>7</v>
@@ -49962,7 +49962,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -49989,7 +49989,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>7</v>
@@ -50042,7 +50042,7 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>7</v>
@@ -50063,7 +50063,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -50090,7 +50090,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -50143,7 +50143,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>8</v>
@@ -50164,7 +50164,7 @@
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -50191,7 +50191,7 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -50244,7 +50244,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>5</v>
@@ -50265,7 +50265,7 @@
         <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -50313,7 +50313,7 @@
         <v>5</v>
       </c>
       <c r="AG27">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:33">
@@ -50345,7 +50345,7 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -50366,7 +50366,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -50414,7 +50414,7 @@
         <v>6</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:33">
@@ -50446,7 +50446,7 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>7</v>
@@ -50467,7 +50467,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -50494,7 +50494,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>8</v>
@@ -50547,7 +50547,7 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -50568,7 +50568,7 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -50648,7 +50648,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -50669,7 +50669,7 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -50696,7 +50696,7 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -50749,7 +50749,7 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>6</v>
@@ -50770,7 +50770,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -50797,7 +50797,7 @@
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>6</v>
@@ -50850,7 +50850,7 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>8</v>
@@ -50871,7 +50871,7 @@
         <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -50898,7 +50898,7 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -50951,7 +50951,7 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>6</v>
@@ -50972,7 +50972,7 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -50999,7 +50999,7 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -51052,7 +51052,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -51073,7 +51073,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -51153,7 +51153,7 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -51174,7 +51174,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -51201,7 +51201,7 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA36">
         <v>7</v>

--- a/Calificaciones20241.xlsx
+++ b/Calificaciones20241.xlsx
@@ -48330,7 +48330,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -48419,7 +48419,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -48440,7 +48440,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -48508,7 +48508,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -48529,7 +48529,7 @@
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -48597,7 +48597,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -48686,7 +48686,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -48775,7 +48775,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -48864,7 +48864,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -48953,7 +48953,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -49042,7 +49042,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -49131,7 +49131,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -49220,7 +49220,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -49309,7 +49309,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -49330,7 +49330,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -49398,7 +49398,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -49419,7 +49419,7 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -49487,7 +49487,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -49576,7 +49576,7 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -49665,7 +49665,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -49754,7 +49754,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -49843,7 +49843,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -49864,7 +49864,7 @@
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -49932,7 +49932,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -50021,7 +50021,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -50110,7 +50110,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -50131,7 +50131,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -50199,7 +50199,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -50220,7 +50220,7 @@
         <v>9</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -50288,7 +50288,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -52372,7 +52372,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -52393,7 +52393,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -52490,7 +52490,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -52579,7 +52579,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -52668,7 +52668,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -52689,7 +52689,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -52757,7 +52757,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -52846,7 +52846,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -52867,7 +52867,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -52935,7 +52935,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -53024,7 +53024,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -53045,7 +53045,7 @@
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -53113,7 +53113,7 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -53202,7 +53202,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -53291,7 +53291,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -53312,7 +53312,7 @@
         <v>6</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -53380,7 +53380,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -53469,7 +53469,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -53490,7 +53490,7 @@
         <v>7</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -53558,7 +53558,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -53647,7 +53647,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -53668,7 +53668,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -53736,7 +53736,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -53825,7 +53825,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -53914,7 +53914,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -54003,7 +54003,7 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -54092,7 +54092,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -54181,7 +54181,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -54202,7 +54202,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
